--- a/Team-Data/2012-13/2-3-2012-13.xlsx
+++ b/Team-Data/2012-13/2-3-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
         <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="H3" t="n">
         <v>49.2</v>
@@ -861,37 +928,37 @@
         <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>80.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M3" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.336</v>
+        <v>0.33</v>
       </c>
       <c r="O3" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="P3" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.782</v>
+        <v>0.78</v>
       </c>
       <c r="R3" t="n">
         <v>8.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T3" t="n">
-        <v>39.5</v>
+        <v>39.8</v>
       </c>
       <c r="U3" t="n">
         <v>23.2</v>
@@ -903,7 +970,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y3" t="n">
         <v>4.8</v>
@@ -912,25 +979,25 @@
         <v>21.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="AC3" t="n">
         <v>-0.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
         <v>15</v>
       </c>
       <c r="AG3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
         <v>1</v>
@@ -951,22 +1018,22 @@
         <v>27</v>
       </c>
       <c r="AN3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
         <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
@@ -981,7 +1048,7 @@
         <v>3</v>
       </c>
       <c r="AX3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -990,7 +1057,7 @@
         <v>26</v>
       </c>
       <c r="BA3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB3" t="n">
         <v>20</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>1.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>10</v>
@@ -1127,10 +1194,10 @@
         <v>18</v>
       </c>
       <c r="AL4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN4" t="n">
         <v>20</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-8.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>29</v>
@@ -1339,7 +1406,7 @@
         <v>30</v>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW5" t="n">
         <v>19</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>2.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF6" t="n">
         <v>8</v>
@@ -1485,7 +1552,7 @@
         <v>25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK6" t="n">
         <v>21</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-5.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
@@ -1679,10 +1746,10 @@
         <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP7" t="n">
         <v>14</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>19</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2043,7 +2110,7 @@
         <v>18</v>
       </c>
       <c r="AN9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2061,7 +2128,7 @@
         <v>10</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -2117,58 +2184,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" t="n">
         <v>18</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G10" t="n">
-        <v>0.375</v>
+        <v>0.383</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J10" t="n">
-        <v>81.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K10" t="n">
         <v>0.446</v>
       </c>
       <c r="L10" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M10" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="N10" t="n">
         <v>0.366</v>
       </c>
       <c r="O10" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P10" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Q10" t="n">
         <v>0.695</v>
       </c>
       <c r="R10" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S10" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T10" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U10" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V10" t="n">
         <v>15.1</v>
@@ -2186,16 +2253,16 @@
         <v>19.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="AC10" t="n">
         <v>-1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2207,13 +2274,13 @@
         <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK10" t="n">
         <v>17</v>
@@ -2228,7 +2295,7 @@
         <v>8</v>
       </c>
       <c r="AO10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2240,7 +2307,7 @@
         <v>7</v>
       </c>
       <c r="AS10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT10" t="n">
         <v>8</v>
@@ -2261,16 +2328,16 @@
         <v>19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB10" t="n">
         <v>22</v>
       </c>
       <c r="BC10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>1.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
         <v>4</v>
@@ -2392,7 +2459,7 @@
         <v>14</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
         <v>8</v>
@@ -2404,13 +2471,13 @@
         <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2440,7 +2507,7 @@
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ11" t="n">
         <v>28</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2677,7 @@
         <v>11</v>
       </c>
       <c r="AU12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2619,7 +2686,7 @@
         <v>5</v>
       </c>
       <c r="AX12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY12" t="n">
         <v>27</v>
@@ -2628,7 +2695,7 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
         <v>2</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>2.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E14" t="n">
         <v>34</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.694</v>
+        <v>0.708</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2875,13 +2942,13 @@
         <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>0.35</v>
+        <v>0.349</v>
       </c>
       <c r="O14" t="n">
         <v>17.1</v>
       </c>
       <c r="P14" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q14" t="n">
         <v>0.706</v>
@@ -2890,7 +2957,7 @@
         <v>11.6</v>
       </c>
       <c r="S14" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T14" t="n">
         <v>41.9</v>
@@ -2899,37 +2966,37 @@
         <v>23.3</v>
       </c>
       <c r="V14" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="W14" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="X14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA14" t="n">
         <v>21.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>100.4</v>
+        <v>100.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG14" t="n">
         <v>3</v>
@@ -2938,7 +3005,7 @@
         <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ14" t="n">
         <v>24</v>
@@ -2950,16 +3017,16 @@
         <v>14</v>
       </c>
       <c r="AM14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO14" t="n">
         <v>11</v>
       </c>
-      <c r="AN14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>12</v>
-      </c>
       <c r="AP14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ14" t="n">
         <v>26</v>
@@ -2977,7 +3044,7 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2989,7 +3056,7 @@
         <v>7</v>
       </c>
       <c r="AZ14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" t="n">
         <v>26</v>
       </c>
       <c r="G15" t="n">
-        <v>0.458</v>
+        <v>0.447</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3048,34 +3115,34 @@
         <v>81.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M15" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="N15" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P15" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S15" t="n">
         <v>33.1</v>
       </c>
       <c r="T15" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U15" t="n">
         <v>22.3</v>
@@ -3084,7 +3151,7 @@
         <v>15.4</v>
       </c>
       <c r="W15" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X15" t="n">
         <v>5.5</v>
@@ -3096,16 +3163,16 @@
         <v>18.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.3</v>
+        <v>102.4</v>
       </c>
       <c r="AC15" t="n">
         <v>1.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>18</v>
@@ -3123,7 +3190,7 @@
         <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK15" t="n">
         <v>10</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO15" t="n">
         <v>4</v>
@@ -3153,22 +3220,22 @@
         <v>3</v>
       </c>
       <c r="AT15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV15" t="n">
         <v>27</v>
       </c>
       <c r="AW15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
         <v>9</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
         <v>5</v>
@@ -3177,7 +3244,7 @@
         <v>1</v>
       </c>
       <c r="BB15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3302,7 +3369,7 @@
         <v>13</v>
       </c>
       <c r="AI16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="n">
         <v>9</v>
@@ -3353,10 +3420,10 @@
         <v>23</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB16" t="n">
         <v>28</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="H17" t="n">
         <v>48.7</v>
@@ -3409,19 +3476,19 @@
         <v>38.5</v>
       </c>
       <c r="J17" t="n">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.49</v>
+        <v>0.489</v>
       </c>
       <c r="L17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="O17" t="n">
         <v>17.1</v>
@@ -3436,13 +3503,13 @@
         <v>8.5</v>
       </c>
       <c r="S17" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T17" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="U17" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V17" t="n">
         <v>13.7</v>
@@ -3460,19 +3527,19 @@
         <v>19.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>102.3</v>
+        <v>102.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AF17" t="n">
         <v>3</v>
@@ -3499,10 +3566,10 @@
         <v>9</v>
       </c>
       <c r="AN17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
         <v>11</v>
@@ -3514,13 +3581,13 @@
         <v>29</v>
       </c>
       <c r="AS17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV17" t="n">
         <v>4</v>
@@ -3535,13 +3602,13 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
         <v>13</v>
       </c>
       <c r="BB17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
@@ -3681,7 +3748,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>23</v>
@@ -3696,7 +3763,7 @@
         <v>4</v>
       </c>
       <c r="AS18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT18" t="n">
         <v>7</v>
@@ -3723,7 +3790,7 @@
         <v>17</v>
       </c>
       <c r="BB18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC18" t="n">
         <v>15</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3975,7 @@
         <v>21</v>
       </c>
       <c r="BC19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
         <v>26</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4270,7 @@
         <v>4</v>
       </c>
       <c r="AF21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG21" t="n">
         <v>5</v>
@@ -4227,13 +4294,13 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ21" t="n">
         <v>19</v>
@@ -4266,7 +4333,7 @@
         <v>10</v>
       </c>
       <c r="BA21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB21" t="n">
         <v>8</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4409,7 +4476,7 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4445,10 +4512,10 @@
         <v>3</v>
       </c>
       <c r="AZ22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
         <v>27</v>
@@ -4600,7 +4667,7 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE24" t="n">
         <v>19</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>25</v>
@@ -4946,7 +5013,7 @@
         <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="n">
         <v>25</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>16</v>
@@ -5125,7 +5192,7 @@
         <v>22</v>
       </c>
       <c r="AJ26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK26" t="n">
         <v>22</v>
@@ -5140,7 +5207,7 @@
         <v>24</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP26" t="n">
         <v>19</v>
@@ -5182,7 +5249,7 @@
         <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5389,7 @@
         <v>15</v>
       </c>
       <c r="AO27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP27" t="n">
         <v>13</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5556,7 @@
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5504,7 +5571,7 @@
         <v>6</v>
       </c>
       <c r="AO28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP28" t="n">
         <v>23</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -5575,85 +5642,85 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E29" t="n">
         <v>17</v>
       </c>
       <c r="F29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>0.354</v>
+        <v>0.362</v>
       </c>
       <c r="H29" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I29" t="n">
-        <v>36.4</v>
+        <v>36.6</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L29" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M29" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O29" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P29" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R29" t="n">
         <v>10.8</v>
       </c>
       <c r="S29" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T29" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U29" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="V29" t="n">
         <v>12.9</v>
       </c>
       <c r="W29" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.5</v>
+        <v>97.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.8</v>
+        <v>-1.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5671,22 +5738,22 @@
         <v>18</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO29" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5704,7 +5771,7 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
@@ -5716,20 +5783,20 @@
         <v>23</v>
       </c>
       <c r="AY29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC29" t="n">
         <v>18</v>
       </c>
-      <c r="BB29" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>21</v>
-      </c>
       <c r="BD29" t="n">
         <v>10</v>
       </c>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
         <v>12</v>
@@ -5871,7 +5938,7 @@
         <v>6</v>
       </c>
       <c r="AP30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ30" t="n">
         <v>12</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6047,7 +6114,7 @@
         <v>17</v>
       </c>
       <c r="AN31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO31" t="n">
         <v>27</v>
@@ -6080,7 +6147,7 @@
         <v>22</v>
       </c>
       <c r="AY31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ31" t="n">
         <v>20</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-3-2012-13</t>
+          <t>2013-02-03</t>
         </is>
       </c>
     </row>
